--- a/JIRA-TICKETS/batch-disbursement/test-cases/valid-data.xlsx
+++ b/JIRA-TICKETS/batch-disbursement/test-cases/valid-data.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Nội dung</t>
   </si>
   <si>
-    <t xml:space="preserve">999</t>
+    <t xml:space="preserve">155</t>
   </si>
   <si>
     <t xml:space="preserve">0120508601T45001</t>
